--- a/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
+++ b/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
@@ -228,7 +228,7 @@
     <t>10.795</t>
   </si>
   <si>
-    <t>1.25A</t>
+    <t>0.8A</t>
   </si>
   <si>
     <t>1808 Fuse / FUSE_0154004</t>
@@ -255,7 +255,7 @@
     <t>12</t>
   </si>
   <si>
-    <t>LGS5145</t>
+    <t>ME3116</t>
   </si>
   <si>
     <t>SOT95P280X110-6N (SOT23-6L)</t>

--- a/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
+++ b/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
@@ -222,16 +222,16 @@
     <t>F1</t>
   </si>
   <si>
-    <t>19.736</t>
-  </si>
-  <si>
-    <t>10.795</t>
+    <t>19.749</t>
+  </si>
+  <si>
+    <t>11.036</t>
   </si>
   <si>
     <t>0.8A</t>
   </si>
   <si>
-    <t>1808 Fuse / FUSE_0154004</t>
+    <t>FUSE-SMD_L10.3-W3.2</t>
   </si>
   <si>
     <t>FB1</t>

--- a/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
+++ b/Hardware/DALI_Load_250W_DigitalLED/JLC_PCBA_CPL-DALI_LOAD_DigitalLED(V0.1).xlsx
@@ -222,10 +222,10 @@
     <t>F1</t>
   </si>
   <si>
-    <t>19.749</t>
-  </si>
-  <si>
-    <t>11.036</t>
+    <t>20.749</t>
+  </si>
+  <si>
+    <t>10.528</t>
   </si>
   <si>
     <t>0.8A</t>
